--- a/instrumentos/sesion-02/Sesion 2.xlsx
+++ b/instrumentos/sesion-02/Sesion 2.xlsx
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B221"/>
+  <dimension ref="A1:B220"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="32" customWidth="1" style="35" min="1" max="1"/>
@@ -2604,7 +2604,7 @@
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" s="35">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -2612,14 +2612,14 @@
           <t>Presentación</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="38" t="inlineStr">
         <is>
           <t>«Buenos días (o buenas tardes). Mi nombre es ________ y colaboro con la tesis de Marcel Trujillo y Alejandro Godoy, estudiante de Ingeniería de Sistemas e Informática de la Universidad de Huánuco.»</t>
         </is>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" s="35">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="47" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -2627,14 +2627,14 @@
           <t>Propósito en una frase</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>«Este estudio busca conocer cómo es su experiencia al buscar noticias de Tu Diario Huánuco desde su celular o computadora.»</t>
         </is>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" s="35">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="46" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -2642,14 +2642,14 @@
           <t>Aclaración: no es evaluación de desempeño</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>«Aquí no se mide qué tan bien lo hace usted: lo que nos interesa es cómo funciona el portal para los lectores.»</t>
         </is>
       </c>
     </row>
     <row r="8" ht="73.5" customHeight="1" s="35">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="47" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -2657,14 +2657,14 @@
           <t>Tiempo disponible</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>«Le pediremos dos búsquedas. Primero, ubicar la noticia sobre el corte del servicio de agua potable en Huánuco, Amarilis y Pillco Marca; después, ubicar el resultado del partido entre Alianza UDH y Bentín Tacna Heroica. Tiene hasta 5 minutos para cada una. Luego responderá dos cuestionarios breves, sin apuro, en unos 10 minutos.»</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" s="35">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="46" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -2672,14 +2672,14 @@
           <t>No hay respuestas correctas ni incorrectas</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>«No hay respuestas correctas ni incorrectas: nos interesa su opinión sincera y su forma habitual de buscar noticias.»</t>
         </is>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" s="35">
-      <c r="A10" s="12" t="n">
+      <c r="A10" s="47" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -2687,14 +2687,14 @@
           <t>Qué hacer ante una duda</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="38" t="inlineStr">
         <is>
           <t>«Sus respuestas son confidenciales. Su nombre y su celular solo se usan para coordinar su participación y se guardan aparte; en los resultados usted aparece únicamente con un código. No le pediremos su DNI. Su participación es voluntaria y puede dejarla en cualquier momento sin ninguna consecuencia.»</t>
         </is>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" s="35">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="46" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -2702,14 +2702,14 @@
           <t>Confidencialidad y código</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t>«Sus respuestas son confidenciales. Su nombre y su celular solo se usan para coordinar su participación y se guardan aparte; en los resultados usted aparece únicamente con un código. No le pediremos su DNI. Su participación es voluntaria y puede dejarla en cualquier momento sin ninguna consecuencia.»</t>
         </is>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" s="35">
-      <c r="A12" s="12" t="n">
+      <c r="A12" s="47" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -2717,7 +2717,7 @@
           <t>Cierre de la aplicación</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>«Con esto terminamos esta primera parte. Más adelante le invitaremos a la segunda parte del estudio, con la nueva plataforma. Muchas gracias por su participación.»</t>
         </is>
@@ -4627,7 +4627,7 @@
       </c>
     </row>
     <row r="5" ht="73.5" customHeight="1" s="35">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -4635,24 +4635,24 @@
           <t>Instrucciones leídas (según guion)</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="38" t="inlineStr">
         <is>
           <t>Guion de la hoja 1, leído completo e idéntico a todos; tareas 1 y 2 en el mismo orden y con las mismas palabras (PDT, anexo 6.2.5).</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>El mismo guion, leído completo e idéntico a todos; solo cambian las dos noticias (tareas 3 y 4, equivalentes), en el mismo orden y con las mismas palabras.</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="6" ht="73.5" customHeight="1" s="35">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="47" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -4660,24 +4660,24 @@
           <t>Tiempo concedido para responder</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>Tareas: máximo 5 minutos (300 s) cada una; si no se encuentra la noticia, se registra 300 s y «no completada». Cuestionarios: sin límite, unos 10 minutos.</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="38" t="inlineStr">
         <is>
           <t>Tareas: máximo 5 minutos (300 s) cada una; si no se encuentra la noticia, se registra 300 s y «no completada». Cuestionarios: sin límite, unos 10 minutos.</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46.5" customHeight="1" s="35">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="46" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -4685,24 +4685,24 @@
           <t>Momento de la jornada (mañana / tarde)</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>Entre las 10:00 y las 13:00 h (mañana) o entre las 16:00 y las 19:00 h (tarde).</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="38" t="inlineStr">
         <is>
           <t>Entre las 10:00 y las 13:00 h (mañana) o entre las 16:00 y las 19:00 h (tarde).</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="E7" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="8" ht="46.5" customHeight="1" s="35">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="47" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -4712,22 +4712,22 @@
       </c>
       <c r="C8" s="38" t="inlineStr">
         <is>
-          <t>De lunes a sábado, dentro de la ventana del pretest (20 al 25/10/2026).</t>
+          <t>De lunes a sábado, dentro de la ventana del pretest (12 al 17/10/2026).</t>
         </is>
       </c>
       <c r="D8" s="38" t="inlineStr">
         <is>
-          <t>De lunes a sábado, dentro de la ventana del postest (03 al 08/11/2026); cada participante repite el mismo día de la semana.</t>
-        </is>
-      </c>
-      <c r="E8" s="24" t="inlineStr">
+          <t>De lunes a sábado, dentro de la ventana del postest (26 al 31/10/2026); cada participante repite el mismo día de la semana.</t>
+        </is>
+      </c>
+      <c r="E8" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1" s="35">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="46" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -4735,24 +4735,24 @@
           <t>Espacio físico o plataforma virtual</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>Virtual, en el dispositivo propio del participante (celular o computadora) y con su conexión habitual. Búsqueda en el portal actual tudiariohuanuco.pe.</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="38" t="inlineStr">
         <is>
           <t>Virtual, en el mismo tipo de dispositivo que usó en el pretest y con su conexión habitual. Búsqueda en la aplicación (chat.tudiariohuanuco.pe), que es la intervención.</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46.5" customHeight="1" s="35">
-      <c r="A10" s="12" t="n">
+      <c r="A10" s="47" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -4760,24 +4760,24 @@
           <t>Presencia o ausencia de jefaturas</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="38" t="inlineStr">
         <is>
           <t>Ausencia de directivos, jefaturas o personal editorial del diario durante las tareas y los cuestionarios.</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="38" t="inlineStr">
         <is>
           <t>Ausencia de directivos, jefaturas o personal editorial del diario durante las tareas y los cuestionarios.</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E10" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1" s="35">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="46" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -4785,24 +4785,24 @@
           <t>Modo de entrega (impreso / digital)</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t>Digital: tareas y cuestionarios presentados en el módulo de gestión del experimento; la búsqueda se hace en el portal actual con el cronómetro del módulo (PDT §1.6 y §3.5.5).</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Digital: tareas y cuestionarios presentados en el módulo de gestión del experimento; la búsqueda se hace en la aplicación con el mismo cronómetro.</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="12" ht="73.5" customHeight="1" s="35">
-      <c r="A12" s="12" t="n">
+      <c r="A12" s="47" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -4810,24 +4810,24 @@
           <t>Fuente del dato (sistema / registro manual)</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>Tiempo: cronómetro del módulo del experimento. Clics: contador instalado en el portal (enlaces, botones y envíos de búsqueda). SUS y satisfacción: respuestas guardadas en el módulo.</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="38" t="inlineStr">
         <is>
           <t>Tiempo: el mismo cronómetro del módulo. Clics: telemetría de la aplicación, con la misma definición de clic (enlaces, botones y envíos de búsqueda). SUS y satisfacción: respuestas guardadas en el módulo.</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E12" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46.5" customHeight="1" s="35">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="46" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -4835,24 +4835,24 @@
           <t>Persona que aplica el instrumento</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="38" t="inlineStr">
         <is>
           <t>Marcel Alexander Javier Trujillo Ávila (tesista) y Alejandro Jeanpier Godoy Condezo (aplicador de apoyo, capacitado en este protocolo).</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>Marcel Alexander Javier Trujillo Ávila (tesista) y Alejandro Jeanpier Godoy Condezo (aplicador de apoyo, capacitado en este protocolo).</t>
         </is>
       </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="E13" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="14" ht="73.5" customHeight="1" s="35">
-      <c r="A14" s="12" t="n">
+      <c r="A14" s="47" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
@@ -4860,24 +4860,24 @@
           <t>Orden de los ítems del instrumento</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="38" t="inlineStr">
         <is>
           <t>Fijo para todos: tarea 1 → tarea 2 → cuestionario SUS (ítems 1 a 10) → cuestionario de satisfacción (ítems 1 a 8), cada uno en el orden del instrumento (PDT, anexo 6.2).</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="38" t="inlineStr">
         <is>
           <t>Fijo para todos: tarea 3 → tarea 4 → cuestionario SUS (ítems 1 a 10) → cuestionario de satisfacción (ítems 1 a 8), cada uno en el orden del instrumento (PDT, anexo 6.2).</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1" s="35">
-      <c r="A15" s="10" t="n">
+      <c r="A15" s="46" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -4885,24 +4885,24 @@
           <t>Unidad de medida del indicador</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="38" t="inlineStr">
         <is>
           <t>Tiempo: segundos; clics: número entero; SUS: puntaje de 0 a 100; satisfacción: escala de Likert de 1 a 5 (puntaje total de 8 a 40).</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="38" t="inlineStr">
         <is>
           <t>Tiempo: segundos; clics: número entero; SUS: puntaje de 0 a 100; satisfacción: escala de Likert de 1 a 5 (puntaje total de 8 a 40).</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1" s="35">
-      <c r="A16" s="12" t="n">
+      <c r="A16" s="47" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -4910,17 +4910,17 @@
           <t>Procedimiento de codificación inmediata</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>Al inscribirse, cada participante recibe un código GU-TDH-###; tiempos, clics y respuestas se guardan solo con ese código. Nombres, apellidos y celular quedan únicamente en el libro de códigos. No se solicita el DNI.</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="38" t="inlineStr">
         <is>
           <t>Al inscribirse, cada participante recibe un código GU-TDH-###; tiempos, clics y respuestas se guardan solo con ese código. Nombres, apellidos y celular quedan únicamente en el libro de códigos. No se solicita el DNI.</t>
         </is>
       </c>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="E16" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -7214,7 +7214,7 @@
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" s="35">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -7222,14 +7222,14 @@
           <t>Nombre del archivo donde se guardó la consulta</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>pretest_extraccion_v1.sql (se guarda en el repositorio del proyecto y en la carpeta de evidencias; no se modifica después de usarla).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="31.5" customHeight="1" s="35">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="47" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>SELECT p.codigo, p.grupo, p.edad, p.zona, p.frec_sem, p.red, r.sus01, …, r.sus10, r.tam01, …, r.tam08, t.t1_seg, t.t1_clics, t.t2_seg, t.t2_clics, r.created_at::date AS fecha_digit FROM thesis_participantes p JOIN thesis_respuestas r ON r.participante_id = p.id AND r.momento = 'pretest' JOIN thesis_tareas t ON t.participante_id = p.id AND t.momento = 'pretest' WHERE p.consentimiento = TRUE AND r.created_at BETWEEN '2026-10-20 00:00' AND '2026-10-25 23:59' ORDER BY p.codigo;  (archivo congelado: pretest_extraccion_v1.sql, hash SHA-256 registrado en la bitácora)</t>
+          <t>SELECT p.codigo, p.grupo, p.edad, p.zona, p.frec_sem, p.red, r.sus01, …, r.sus10, r.tam01, …, r.tam08, t.t1_seg, t.t1_clics, t.t2_seg, t.t2_clics, r.created_at::date AS fecha_digit FROM thesis_participantes p JOIN thesis_respuestas r ON r.participante_id = p.id AND r.momento = 'pretest' JOIN thesis_tareas t ON t.participante_id = p.id AND t.momento = 'pretest' WHERE p.consentimiento = TRUE AND r.created_at BETWEEN '2026-10-12 00:00' AND '2026-10-17 23:59' ORDER BY p.codigo;  (archivo congelado: pretest_extraccion_v1.sql, hash SHA-256 registrado en la bitácora)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="33" customHeight="1" s="35">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="46" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -7252,14 +7252,14 @@
           <t>Sistema o base de datos de origen</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>PostgreSQL (Supabase): tablas thesis_* del microservicio Thesis (participantes, tareas, tiempos y respuestas del SUS y de satisfacción). Clics del pretest: contador instalado en el portal tudiariohuanuco.pe.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="31.5" customHeight="1" s="35">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="47" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="C8" s="39" t="inlineStr">
         <is>
-          <t>Etiqueta v1.3.2 del repositorio (vigente del 20 al 25/10/2026 para el pretest); la versión de la intervención se congeló el 26/10/2026 como v1.4.0.</t>
+          <t>Etiqueta v1.3.2 del repositorio (vigente del 12 al 17/10/2026 para el pretest); la versión de la intervención se congeló el 18/10/2026 como v1.0.0-frozen-2026-10-18.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="31.5" customHeight="1" s="35">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="46" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="C9" s="39" t="inlineStr">
         <is>
-          <t>26/10/2026, 09:00 (hora de Lima), al día siguiente del cierre del pretest.</t>
+          <t>18/10/2026, 09:00 (hora de Lima), al día siguiente del cierre del pretest.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="33" customHeight="1" s="35">
-      <c r="A10" s="12" t="n">
+      <c r="A10" s="47" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="C10" s="38" t="inlineStr">
         <is>
-          <t>20/10/2026 – 25/10/2026 (ventana del pretest; cuaderno de la Sesión 01, hoja 3, actividad 9).</t>
+          <t>12/10/2026 – 17/10/2026 (ventana del pretest; cuaderno de la Sesión 01, hoja 3, actividad 9).</t>
         </is>
       </c>
     </row>
     <row r="11" ht="31.5" customHeight="1" s="35">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="46" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -7312,14 +7312,14 @@
           <t>Número de días hábiles incluidos</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>6 días corridos (del martes 20 al domingo 25/10/2026), de los cuales 4 son hábiles (20, 21, 22 y 23/10/2026).</t>
+      <c r="C11" s="38" t="inlineStr">
+        <is>
+          <t>6 días corridos (del lunes 12 al sábado 17/10/2026), de los cuales 5 son hábiles (12, 13, 14, 15 y 16/10/2026).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="31.5" customHeight="1" s="35">
-      <c r="A12" s="12" t="n">
+      <c r="A12" s="47" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -7327,14 +7327,14 @@
           <t>Momento del ciclo (inicio / quincena / fin de mes)</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Fin de la tercera semana de octubre: semana ordinaria, sin feriados ni campañas especiales del diario.</t>
+      <c r="C12" s="38" t="inlineStr">
+        <is>
+          <t>Semana del 12 al 17 de octubre: semana ordinaria, sin feriados ni campañas especiales del diario.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46.5" customHeight="1" s="35">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="46" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -7342,14 +7342,14 @@
           <t>Criterios de inclusión aplicados en el filtro</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="38" t="inlineStr">
         <is>
           <t>Participantes con consentimiento aceptado que cumplen los criterios de inclusión: mayores de 18 años, leen el portal más de 2 veces por semana, acceden habitualmente desde dispositivos móviles.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46.5" customHeight="1" s="35">
-      <c r="A14" s="12" t="n">
+      <c r="A14" s="47" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -7357,14 +7357,14 @@
           <t>Criterios de exclusión aplicados en el filtro</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="38" t="inlineStr">
         <is>
           <t>Personal técnico, administrativo o de redacción del diario; personas con discapacidad cognitiva o visual severa que les impida completar las tareas; registros de participantes que se retiraron.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="31.5" customHeight="1" s="35">
-      <c r="A15" s="10" t="n">
+      <c r="A15" s="46" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -7372,14 +7372,14 @@
           <t>Unidad de medida del indicador</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="38" t="inlineStr">
         <is>
           <t>Tiempo de búsqueda en segundos; número de clics (unidades); SUS de 0 a 100; satisfacción de 8 a 40.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="31.5" customHeight="1" s="35">
-      <c r="A16" s="12" t="n">
+      <c r="A16" s="47" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
     </row>
     <row r="17" ht="31.5" customHeight="1" s="35">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="46" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="C17" s="39" t="inlineStr">
         <is>
-          <t>Captura captura_extraccion_pretest_2026-10-26.png con la fecha y la hora visibles, archivada en la carpeta de evidencias.</t>
+          <t>Captura captura_extraccion_pretest_2026-10-18.png con la fecha y la hora visibles, archivada en la carpeta de evidencias.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="31.5" customHeight="1" s="35">
-      <c r="A18" s="12" t="n">
+      <c r="A18" s="47" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -7417,7 +7417,7 @@
           <t>Persona de TI que autorizó o ejecutó el acceso</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="39" t="inlineStr">
         <is>
           <t>Ejecuta: Marcel Alexander Javier Trujillo Ávila (desarrollador del sistema). Autoriza: Gerencia de Tu Diario Huánuco (carta de autorización del 10/07/2026).</t>
         </is>
@@ -9305,7 +9305,7 @@
           <t>La autorización institucional está vigente para la fecha de aplicación</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9325,7 +9325,7 @@
           <t>Se verificó la firma del consentimiento de CADA participante antes de entregar el instrumento</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9345,7 +9345,7 @@
           <t>Los instrumentos son la versión definitiva y validada, sin modificaciones</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9365,7 +9365,7 @@
           <t>Hay instrumentos suficientes más un 20 % de reserva</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9385,7 +9385,7 @@
           <t>El guion de aplicación está impreso y a la mano</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9405,14 +9405,14 @@
           <t>El libro de códigos está disponible y actualizado</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
       <c r="D11" s="38" t="inlineStr">
         <is>
-          <t>Libro de códigos actualizado al 19/10/2026 (126 inscritos).</t>
+          <t>Libro de códigos actualizado al 11/10/2026 (126 inscritos).</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
           <t>El acta y el registro de incidencias están en blanco y listos</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9455,7 +9455,7 @@
           <t>El espacio está reservado y confirmado con la institución</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9475,7 +9475,7 @@
           <t>No hay jefaturas presentes ni circulando durante la aplicación</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9495,7 +9495,7 @@
           <t>El ambiente permite responder sin interferencias externas</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9515,14 +9515,14 @@
           <t>Los equipos tecnológicos fueron probados antes de iniciar</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
       <c r="D17" s="38" t="inlineStr">
         <is>
-          <t>Módulo, cronómetro y contador de clics probados el 19/10/2026.</t>
+          <t>Módulo, cronómetro y contador de clics probados el 11/10/2026.</t>
         </is>
       </c>
     </row>
@@ -9535,7 +9535,7 @@
           <t>La disposición del espacio evita que los participantes vean respuestas ajenas</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9565,7 +9565,7 @@
           <t>Se leyó el guion completo, sin agregar ni omitir</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9585,7 +9585,7 @@
           <t>Se leyeron las mismas instrucciones a todos los subgrupos</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9605,7 +9605,7 @@
           <t>Ante dudas se repitió el ítem sin parafrasear ni ejemplificar</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9625,7 +9625,7 @@
           <t>Se concedió el mismo tiempo a todos los participantes</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9645,7 +9645,7 @@
           <t>Se controló la hora de inicio y de término</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9665,7 +9665,7 @@
           <t>Se dio el mismo trato y acompañamiento a todos, sin excepción por jerarquía</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C25" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9685,7 +9685,7 @@
           <t>Se registraron las incidencias en el momento en que ocurrieron</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C26" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9715,7 +9715,7 @@
           <t>Los instrumentos se codificaron ANTES de retirarse del lugar</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C28" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9735,7 +9735,7 @@
           <t>Se verificó que no hubiera instrumentos sin código</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9755,7 +9755,7 @@
           <t>Se contó el número de instrumentos recogidos y coincide con el registro</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9775,7 +9775,7 @@
           <t>Los instrumentos se guardaron en sobre o carpeta cerrada</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C31" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9795,7 +9795,7 @@
           <t>Se levantó el acta de aplicación el mismo día</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C32" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9815,7 +9815,7 @@
           <t>Se obtuvo la firma de la contraparte institucional en el acta</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9845,14 +9845,14 @@
           <t>Los datos se digitaron en la base codificada dentro de las 48 horas</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C35" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
       <c r="D35" s="38" t="inlineStr">
         <is>
-          <t>Exportación el 26/10/2026, dentro de las 48 horas posteriores al cierre.</t>
+          <t>Exportación el 18/10/2026, dentro de las 48 horas posteriores al cierre.</t>
         </is>
       </c>
     </row>
@@ -9865,7 +9865,7 @@
           <t>Se verificó por doble digitación al menos el 20 % de los registros</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C36" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9885,7 +9885,7 @@
           <t>Se revisaron datos faltantes y valores atípicos</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C37" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9905,7 +9905,7 @@
           <t>La base se respaldó en dos ubicaciones, una fuera del equipo principal</t>
         </is>
       </c>
-      <c r="C38" s="24" t="inlineStr">
+      <c r="C38" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9925,7 +9925,7 @@
           <t>El archivo está cifrado o protegido con contraseña</t>
         </is>
       </c>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="C39" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -9945,7 +9945,7 @@
           <t>Los instrumentos físicos quedaron bajo llave</t>
         </is>
       </c>
-      <c r="C40" s="24" t="inlineStr">
+      <c r="C40" s="45" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -12093,7 +12093,7 @@
       </c>
     </row>
     <row r="5" ht="25.5" customHeight="1" s="35">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -12106,8 +12106,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="24" t="n"/>
+      <c r="D5" s="45" t="n"/>
+      <c r="E5" s="45" t="n"/>
       <c r="F5" s="38" t="inlineStr">
         <is>
           <t>Se presenta e indica la universidad y el propósito.</t>
@@ -12115,7 +12115,7 @@
       </c>
     </row>
     <row r="6" ht="25.5" customHeight="1" s="35">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="47" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -12128,12 +12128,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="D6" s="24" t="n"/>
-      <c r="E6" s="24" t="n"/>
+      <c r="D6" s="45" t="n"/>
+      <c r="E6" s="45" t="n"/>
       <c r="F6" s="25" t="n"/>
     </row>
     <row r="7" ht="25.5" customHeight="1" s="35">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="46" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -12146,8 +12146,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="D7" s="24" t="n"/>
-      <c r="E7" s="24" t="n"/>
+      <c r="D7" s="45" t="n"/>
+      <c r="E7" s="45" t="n"/>
       <c r="F7" s="38" t="inlineStr">
         <is>
           <t>Lectura textual del guion.</t>
@@ -12155,7 +12155,7 @@
       </c>
     </row>
     <row r="8" ht="25.5" customHeight="1" s="35">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="47" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -12168,12 +12168,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="D8" s="24" t="n"/>
-      <c r="E8" s="24" t="n"/>
+      <c r="D8" s="45" t="n"/>
+      <c r="E8" s="45" t="n"/>
       <c r="F8" s="25" t="n"/>
     </row>
     <row r="9" ht="25.5" customHeight="1" s="35">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="46" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -12186,12 +12186,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="D9" s="24" t="n"/>
-      <c r="E9" s="24" t="n"/>
+      <c r="D9" s="45" t="n"/>
+      <c r="E9" s="45" t="n"/>
       <c r="F9" s="25" t="n"/>
     </row>
     <row r="10" ht="25.5" customHeight="1" s="35">
-      <c r="A10" s="12" t="n">
+      <c r="A10" s="47" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -12199,13 +12199,13 @@
           <t>Aclara que no es una evaluación de desempeño</t>
         </is>
       </c>
-      <c r="C10" s="24" t="n"/>
+      <c r="C10" s="45" t="n"/>
       <c r="D10" s="44" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E10" s="24" t="n"/>
+      <c r="E10" s="45" t="n"/>
       <c r="F10" s="38" t="inlineStr">
         <is>
           <t>Lo aclaró, pero no en todas las sesiones al inicio.</t>
@@ -12213,7 +12213,7 @@
       </c>
     </row>
     <row r="11" ht="25.5" customHeight="1" s="35">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="46" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -12226,12 +12226,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="24" t="n"/>
+      <c r="D11" s="45" t="n"/>
+      <c r="E11" s="45" t="n"/>
       <c r="F11" s="25" t="n"/>
     </row>
     <row r="12" ht="25.5" customHeight="1" s="35">
-      <c r="A12" s="12" t="n">
+      <c r="A12" s="47" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -12244,8 +12244,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="24" t="n"/>
+      <c r="D12" s="45" t="n"/>
+      <c r="E12" s="45" t="n"/>
       <c r="F12" s="38" t="inlineStr">
         <is>
           <t>No mira la pantalla del participante (sesión por videollamada).</t>
@@ -12253,7 +12253,7 @@
       </c>
     </row>
     <row r="13" ht="25.5" customHeight="1" s="35">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="46" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -12266,12 +12266,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="D13" s="24" t="n"/>
-      <c r="E13" s="24" t="n"/>
+      <c r="D13" s="45" t="n"/>
+      <c r="E13" s="45" t="n"/>
       <c r="F13" s="25" t="n"/>
     </row>
     <row r="14" ht="25.5" customHeight="1" s="35">
-      <c r="A14" s="12" t="n">
+      <c r="A14" s="47" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
@@ -12284,12 +12284,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="D14" s="24" t="n"/>
-      <c r="E14" s="24" t="n"/>
+      <c r="D14" s="45" t="n"/>
+      <c r="E14" s="45" t="n"/>
       <c r="F14" s="25" t="n"/>
     </row>
     <row r="15" ht="25.5" customHeight="1" s="35">
-      <c r="A15" s="10" t="n">
+      <c r="A15" s="46" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -12302,12 +12302,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="D15" s="24" t="n"/>
-      <c r="E15" s="24" t="n"/>
+      <c r="D15" s="45" t="n"/>
+      <c r="E15" s="45" t="n"/>
       <c r="F15" s="25" t="n"/>
     </row>
     <row r="16" ht="25.5" customHeight="1" s="35">
-      <c r="A16" s="12" t="n">
+      <c r="A16" s="47" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -12320,12 +12320,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="D16" s="24" t="n"/>
-      <c r="E16" s="24" t="n"/>
+      <c r="D16" s="45" t="n"/>
+      <c r="E16" s="45" t="n"/>
       <c r="F16" s="25" t="n"/>
     </row>
     <row r="17" ht="25.5" customHeight="1" s="35">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="46" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -12333,13 +12333,13 @@
           <t>Anota las incidencias en el momento en que ocurren</t>
         </is>
       </c>
-      <c r="C17" s="24" t="n"/>
+      <c r="C17" s="45" t="n"/>
       <c r="D17" s="44" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E17" s="24" t="n"/>
+      <c r="E17" s="45" t="n"/>
       <c r="F17" s="38" t="inlineStr">
         <is>
           <t>Dos incidencias se anotaron minutos después.</t>
@@ -12347,7 +12347,7 @@
       </c>
     </row>
     <row r="18" ht="25.5" customHeight="1" s="35">
-      <c r="A18" s="12" t="n">
+      <c r="A18" s="47" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -12360,8 +12360,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="D18" s="24" t="n"/>
-      <c r="E18" s="24" t="n"/>
+      <c r="D18" s="45" t="n"/>
+      <c r="E18" s="45" t="n"/>
       <c r="F18" s="25" t="n"/>
     </row>
     <row r="19">
@@ -14888,11 +14888,11 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" s="35">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="34" t="n">
-        <v>46315</v>
+        <v>46307</v>
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
@@ -14921,11 +14921,11 @@
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="35">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="47" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="34" t="n">
-        <v>46315</v>
+        <v>46307</v>
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
@@ -14954,11 +14954,11 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="35">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="46" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="34" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
@@ -14987,11 +14987,11 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="35">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="47" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="34" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
       <c r="C8" s="25" t="inlineStr">
         <is>
@@ -15020,11 +15020,11 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" s="35">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="46" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="34" t="n">
-        <v>46317</v>
+        <v>46309</v>
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
@@ -15053,11 +15053,11 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" s="35">
-      <c r="A10" s="12" t="n">
+      <c r="A10" s="47" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="34" t="n">
-        <v>46318</v>
+        <v>46310</v>
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
@@ -15086,11 +15086,11 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="35">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="46" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="34" t="n">
-        <v>46318</v>
+        <v>46310</v>
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
@@ -15119,11 +15119,11 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" s="35">
-      <c r="A12" s="12" t="n">
+      <c r="A12" s="47" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="34" t="n">
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
@@ -15152,11 +15152,11 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" s="35">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="46" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="34" t="n">
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
@@ -15185,11 +15185,11 @@
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" s="35">
-      <c r="A14" s="12" t="n">
+      <c r="A14" s="47" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="34" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="35">
-      <c r="A15" s="10" t="n">
+      <c r="A15" s="46" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="34" t="n"/>
@@ -15229,7 +15229,7 @@
       <c r="G15" s="25" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1" s="35">
-      <c r="A16" s="12" t="n">
+      <c r="A16" s="47" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="34" t="n"/>
@@ -15240,7 +15240,7 @@
       <c r="G16" s="25" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1" s="35">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="46" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="34" t="n"/>
@@ -15251,7 +15251,7 @@
       <c r="G17" s="25" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1" s="35">
-      <c r="A18" s="12" t="n">
+      <c r="A18" s="47" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="34" t="n"/>
@@ -15262,7 +15262,7 @@
       <c r="G18" s="25" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1" s="35">
-      <c r="A19" s="10" t="n">
+      <c r="A19" s="46" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="34" t="n"/>
@@ -15273,7 +15273,7 @@
       <c r="G19" s="25" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1" s="35">
-      <c r="A20" s="12" t="n">
+      <c r="A20" s="47" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="34" t="n"/>
@@ -15284,7 +15284,7 @@
       <c r="G20" s="25" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1" s="35">
-      <c r="A21" s="10" t="n">
+      <c r="A21" s="46" t="n">
         <v>17</v>
       </c>
       <c r="B21" s="34" t="n"/>
@@ -15295,7 +15295,7 @@
       <c r="G21" s="25" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1" s="35">
-      <c r="A22" s="12" t="n">
+      <c r="A22" s="47" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="34" t="n"/>
@@ -15306,7 +15306,7 @@
       <c r="G22" s="25" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1" s="35">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="46" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="34" t="n"/>
@@ -15317,7 +15317,7 @@
       <c r="G23" s="25" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1" s="35">
-      <c r="A24" s="12" t="n">
+      <c r="A24" s="47" t="n">
         <v>20</v>
       </c>
       <c r="B24" s="34" t="n"/>
@@ -24617,7 +24617,7 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" s="35">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="46" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -24625,12 +24625,12 @@
           <t>Guion de aplicación en versión final</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="C5" s="45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D5" s="46" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -24642,7 +24642,7 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" s="35">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="47" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -24650,12 +24650,12 @@
           <t>Ficha de condiciones estandarizadas firmada</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="C6" s="45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D6" s="47" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -24667,7 +24667,7 @@
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" s="35">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="46" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -24675,24 +24675,24 @@
           <t>Acta de aplicación con firma de la contraparte</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="C7" s="45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D7" s="46" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
       <c r="E7" s="38" t="inlineStr">
         <is>
-          <t>Actas del 20 al 25/10/2026; la del cierre firmada por la Gerencia del diario.</t>
+          <t>Actas del 12 al 17/10/2026; la del cierre firmada por la Gerencia del diario.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" s="35">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="47" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -24700,12 +24700,12 @@
           <t>Registro de incidencias de la jornada</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="C8" s="45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D8" s="47" t="inlineStr">
         <is>
           <t>PDF / XLSX</t>
         </is>
@@ -24717,7 +24717,7 @@
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" s="35">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="46" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -24725,12 +24725,12 @@
           <t>Lista de cotejo de aplicación completada</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="C9" s="45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D9" s="46" t="inlineStr">
         <is>
           <t>XLSX</t>
         </is>
@@ -24742,7 +24742,7 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" s="35">
-      <c r="A10" s="12" t="n">
+      <c r="A10" s="47" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -24750,12 +24750,12 @@
           <t>Ficha de observación del compañero o del docente</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="C10" s="45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D10" s="47" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -24767,7 +24767,7 @@
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" s="35">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="46" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -24775,12 +24775,12 @@
           <t>Instrumentos aplicados, escaneados y codificados</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="45" t="inlineStr">
         <is>
           <t>No aplica</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="46" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -24792,7 +24792,7 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" s="35">
-      <c r="A12" s="12" t="n">
+      <c r="A12" s="47" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -24800,12 +24800,12 @@
           <t>Consentimientos informados firmados</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="C12" s="45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D12" s="47" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -24817,7 +24817,7 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" s="35">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="46" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -24825,12 +24825,12 @@
           <t>Base de datos del pretest, codificada</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="C13" s="45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D13" s="46" t="inlineStr">
         <is>
           <t>XLSX</t>
         </is>
@@ -24842,7 +24842,7 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" s="35">
-      <c r="A14" s="12" t="n">
+      <c r="A14" s="47" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
@@ -24850,12 +24850,12 @@
           <t>Archivo con la consulta de extracción congelada</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="C14" s="45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D14" s="47" t="inlineStr">
         <is>
           <t>SQL / TXT</t>
         </is>
@@ -24867,7 +24867,7 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" s="35">
-      <c r="A15" s="10" t="n">
+      <c r="A15" s="46" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -24875,24 +24875,24 @@
           <t>Captura del reporte del sistema con fecha visible</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="C15" s="45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D15" s="46" t="inlineStr">
         <is>
           <t>PNG / PDF</t>
         </is>
       </c>
       <c r="E15" s="38" t="inlineStr">
         <is>
-          <t>captura_extraccion_pretest_2026-10-26.png</t>
+          <t>captura_extraccion_pretest_2026-10-18.png</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" s="35">
-      <c r="A16" s="12" t="n">
+      <c r="A16" s="47" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -24900,12 +24900,12 @@
           <t>Evidencia fotográfica de la aplicación (autorizada)</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="45" t="inlineStr">
         <is>
           <t>No aplica</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="47" t="inlineStr">
         <is>
           <t>PNG</t>
         </is>
@@ -24917,7 +24917,7 @@
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" s="35">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="46" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -24925,12 +24925,12 @@
           <t>Constancia de respaldo en dos ubicaciones</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="C17" s="45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D17" s="46" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -24942,7 +24942,7 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" s="35">
-      <c r="A18" s="12" t="n">
+      <c r="A18" s="47" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -24950,12 +24950,12 @@
           <t>Control de trazabilidad completado</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="C18" s="45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D18" s="47" t="inlineStr">
         <is>
           <t>XLSX</t>
         </is>
